--- a/data/trans_bre/P29A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P29A_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-42,08; -32,49</t>
+          <t>-42,0; -31,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-40,75; -30,76</t>
+          <t>-41,06; -30,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,75; -29,46</t>
+          <t>-39,71; -29,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,25; -24,33</t>
+          <t>-34,08; -23,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,59; -55,55</t>
+          <t>-66,68; -54,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-68,1; -55,81</t>
+          <t>-68,32; -55,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-63,12; -51,07</t>
+          <t>-63,02; -50,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-61,01; -48,43</t>
+          <t>-60,81; -47,81</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,39; -27,7</t>
+          <t>-36,84; -28,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,98; -26,64</t>
+          <t>-34,73; -26,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,7; -20,82</t>
+          <t>-29,63; -20,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,59; 0,62</t>
+          <t>-30,8; 0,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,24; -49,23</t>
+          <t>-60,73; -50,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,04; -49,64</t>
+          <t>-60,7; -49,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,05; -40,52</t>
+          <t>-52,82; -39,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,77; -0,36</t>
+          <t>-60,06; 4,12</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-32,4; -22,91</t>
+          <t>-32,64; -21,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-37,65; -27,09</t>
+          <t>-37,68; -27,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,54; -21,56</t>
+          <t>-31,6; -21,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,6; 28,04</t>
+          <t>-24,66; 23,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-67,43; -53,78</t>
+          <t>-67,19; -51,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,06; -50,6</t>
+          <t>-64,37; -50,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-55,01; -41,34</t>
+          <t>-55,33; -41,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-51,95; 63,71</t>
+          <t>-51,99; 53,92</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,72; -21,05</t>
+          <t>-29,91; -21,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,68; -21,15</t>
+          <t>-30,09; -21,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,98; -17,68</t>
+          <t>-26,69; -17,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,55; -16,95</t>
+          <t>-27,78; -16,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,45; -41,06</t>
+          <t>-53,28; -41,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,95; -38,49</t>
+          <t>-51,07; -39,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,15; -30,62</t>
+          <t>-42,76; -30,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,06; -37,23</t>
+          <t>-56,56; -36,59</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-32,71; -28,28</t>
+          <t>-32,58; -27,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-32,76; -27,95</t>
+          <t>-32,8; -28,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,68; -23,9</t>
+          <t>-28,88; -23,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,43; -1,38</t>
+          <t>-24,35; -3,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-58,35; -52,46</t>
+          <t>-58,29; -52,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-57,11; -50,79</t>
+          <t>-57,27; -51,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-49,13; -42,69</t>
+          <t>-49,35; -42,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,25; -2,74</t>
+          <t>-50,72; -7,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P29A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P29A_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-28,95</t>
+          <t>-27,76</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-55,03%</t>
+          <t>-54,07%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-42,0; -31,97</t>
+          <t>-41,99; -32,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-41,06; -30,45</t>
+          <t>-40,74; -30,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,71; -29,38</t>
+          <t>-39,57; -29,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,08; -23,69</t>
+          <t>-32,42; -22,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,68; -54,82</t>
+          <t>-66,37; -54,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-68,32; -55,54</t>
+          <t>-68,02; -54,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-63,02; -50,36</t>
+          <t>-62,72; -50,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,81; -47,81</t>
+          <t>-59,61; -46,76</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-18,96</t>
+          <t>-27,02</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-47,37%</t>
+          <t>-56,4%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,84; -28,26</t>
+          <t>-36,71; -28,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,73; -26,19</t>
+          <t>-35,42; -26,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,63; -20,63</t>
+          <t>-29,82; -21,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 0,92</t>
+          <t>-31,05; -22,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,73; -50,37</t>
+          <t>-60,69; -49,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,7; -49,2</t>
+          <t>-61,36; -49,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,82; -39,65</t>
+          <t>-52,85; -40,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,06; 4,12</t>
+          <t>-61,46; -49,59</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-6,1</t>
+          <t>-20,34</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-13,12%</t>
+          <t>-45,02%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-32,64; -21,9</t>
+          <t>-32,59; -22,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-37,68; -27,13</t>
+          <t>-37,47; -27,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,6; -21,71</t>
+          <t>-31,61; -21,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 23,55</t>
+          <t>-25,37; -15,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-67,19; -51,96</t>
+          <t>-67,53; -53,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,37; -50,69</t>
+          <t>-63,69; -50,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-55,33; -41,11</t>
+          <t>-55,51; -41,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-51,99; 53,92</t>
+          <t>-52,59; -36,1</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-21,23</t>
+          <t>-19,24</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-44,3%</t>
+          <t>-40,86%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,91; -21,34</t>
+          <t>-29,59; -21,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,09; -21,04</t>
+          <t>-29,92; -20,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,69; -17,89</t>
+          <t>-26,62; -17,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,78; -16,47</t>
+          <t>-23,3; -15,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,28; -41,22</t>
+          <t>-53,5; -41,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,07; -39,03</t>
+          <t>-50,69; -38,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,76; -30,71</t>
+          <t>-43,01; -30,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,56; -36,59</t>
+          <t>-47,0; -33,63</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-17,61</t>
+          <t>-23,37</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-38,49%</t>
+          <t>-48,96%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-32,58; -27,95</t>
+          <t>-32,84; -28,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-32,8; -28,13</t>
+          <t>-32,73; -28,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,88; -23,99</t>
+          <t>-28,87; -23,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,35; -3,41</t>
+          <t>-25,36; -20,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-58,29; -52,1</t>
+          <t>-58,51; -52,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-57,27; -51,17</t>
+          <t>-56,98; -50,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-49,35; -42,69</t>
+          <t>-49,33; -42,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,72; -7,52</t>
+          <t>-51,99; -45,27</t>
         </is>
       </c>
     </row>
